--- a/docs/reports/daily/ER_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/ER_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +207,13 @@
     <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -229,7 +229,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +244,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,6 +309,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -714,7 +732,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -857,19 +874,19 @@
         <f>'Daily Breakdown'!J45</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="46">
         <f>IFERROR(G5/D5,0)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="47">
         <f>IFERROR(G5/E5,0)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="48">
         <f>IFERROR(G5/E5*100,0)</f>
         <v/>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="47">
         <f>IFERROR(G5/(D5*E5/1000),0)</f>
         <v/>
       </c>
@@ -877,19 +894,19 @@
         <f>'Daily Breakdown'!K45</f>
         <v/>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="46">
         <f>IFERROR(N5/D5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="47">
         <f>IFERROR(N5/E5,0)</f>
         <v/>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="47">
         <f>IFERROR(N5/(D5*E5/100),0)</f>
         <v/>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="48">
         <f>IFERROR(N5/E5*100,0)</f>
         <v/>
       </c>
@@ -939,7 +956,13 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Availability base excludes locos with FS+OS pkts = 0 (they are still listed below; only the Total-pkts availability base drops them).</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1011,7 +1034,7 @@
       <c r="C4" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="49" t="n">
         <v>244.02</v>
       </c>
       <c r="E4" s="18" t="n">
@@ -1051,7 +1074,7 @@
       <c r="C5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="49" t="n">
         <v>244.02</v>
       </c>
       <c r="E5" s="18" t="n">
@@ -1091,7 +1114,7 @@
       <c r="C6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="49" t="n">
         <v>243.76</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -1131,7 +1154,7 @@
       <c r="C7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="49" t="n">
         <v>243.68</v>
       </c>
       <c r="E7" s="18" t="n">
@@ -1171,7 +1194,7 @@
       <c r="C8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="49" t="n">
         <v>243.91</v>
       </c>
       <c r="E8" s="18" t="n">
@@ -1211,7 +1234,7 @@
       <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="49" t="n">
         <v>199.74</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -1251,7 +1274,7 @@
       <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="49" t="n">
         <v>199.74</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -1291,7 +1314,7 @@
       <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="49" t="n">
         <v>93.70999999999999</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -1331,7 +1354,7 @@
       <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="49" t="n">
         <v>232.19</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -1371,7 +1394,7 @@
       <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="49" t="n">
         <v>199.19</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -1411,7 +1434,7 @@
       <c r="C14" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="49" t="n">
         <v>207.95</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -1451,7 +1474,7 @@
       <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="49" t="n">
         <v>232.22</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -1491,7 +1514,7 @@
       <c r="C16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -1531,7 +1554,7 @@
       <c r="C17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="49" t="n">
         <v>199.05</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -1571,7 +1594,7 @@
       <c r="C18" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="49" t="n">
         <v>10.37</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -1611,7 +1634,7 @@
       <c r="C19" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="49" t="n">
         <v>235.52</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -1651,7 +1674,7 @@
       <c r="C20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="49" t="n">
         <v>231.65</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -1691,7 +1714,7 @@
       <c r="C21" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="49" t="n">
         <v>231.65</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -1731,7 +1754,7 @@
       <c r="C22" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="49" t="n">
         <v>199.53</v>
       </c>
       <c r="E22" s="18" t="n">
@@ -1771,7 +1794,7 @@
       <c r="C23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="49" t="n">
         <v>224.78</v>
       </c>
       <c r="E23" s="18" t="n">
@@ -1811,7 +1834,7 @@
       <c r="C24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="49" t="n">
         <v>232.25</v>
       </c>
       <c r="E24" s="18" t="n">
@@ -1851,7 +1874,7 @@
       <c r="C25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="49" t="n">
         <v>231.63</v>
       </c>
       <c r="E25" s="18" t="n">
@@ -1891,7 +1914,7 @@
       <c r="C26" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="49" t="n">
         <v>208.41</v>
       </c>
       <c r="E26" s="18" t="n">
@@ -1931,7 +1954,7 @@
       <c r="C27" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="49" t="n">
         <v>199.39</v>
       </c>
       <c r="E27" s="18" t="n">
@@ -1971,7 +1994,7 @@
       <c r="C28" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="49" t="n">
         <v>199.4</v>
       </c>
       <c r="E28" s="18" t="n">
@@ -2011,7 +2034,7 @@
       <c r="C29" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="49" t="n">
         <v>82.52</v>
       </c>
       <c r="E29" s="18" t="n">
@@ -2051,7 +2074,7 @@
       <c r="C30" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="49" t="n">
         <v>156.87</v>
       </c>
       <c r="E30" s="18" t="n">
@@ -2091,7 +2114,7 @@
       <c r="C31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="49" t="n">
         <v>93.98999999999999</v>
       </c>
       <c r="E31" s="18" t="n">
@@ -2131,7 +2154,7 @@
       <c r="C32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="49" t="n">
         <v>94.13</v>
       </c>
       <c r="E32" s="18" t="n">
@@ -2171,7 +2194,7 @@
       <c r="C33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="49" t="n">
         <v>81.39</v>
       </c>
       <c r="E33" s="18" t="n">
@@ -2211,7 +2234,7 @@
       <c r="C34" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="49" t="n">
         <v>94.19</v>
       </c>
       <c r="E34" s="18" t="n">
@@ -2251,7 +2274,7 @@
       <c r="C35" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="49" t="n">
         <v>82.54000000000001</v>
       </c>
       <c r="E35" s="18" t="n">
@@ -2291,7 +2314,7 @@
       <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D36" s="49" t="n">
         <v>81.68000000000001</v>
       </c>
       <c r="E36" s="18" t="n">
@@ -2331,7 +2354,7 @@
       <c r="C37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="17" t="n">
+      <c r="D37" s="49" t="n">
         <v>92.67</v>
       </c>
       <c r="E37" s="18" t="n">
@@ -2371,7 +2394,7 @@
       <c r="C38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="17" t="n">
+      <c r="D38" s="49" t="n">
         <v>60.41</v>
       </c>
       <c r="E38" s="18" t="n">
@@ -2411,7 +2434,7 @@
       <c r="C39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="17" t="n">
+      <c r="D39" s="49" t="n">
         <v>0.62</v>
       </c>
       <c r="E39" s="18" t="n">
@@ -2451,7 +2474,7 @@
       <c r="C40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="17" t="n">
+      <c r="D40" s="49" t="n">
         <v>0.9</v>
       </c>
       <c r="E40" s="18" t="n">
@@ -2491,7 +2514,7 @@
       <c r="C41" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="17" t="n">
+      <c r="D41" s="49" t="n">
         <v>232.04</v>
       </c>
       <c r="E41" s="18" t="n">
@@ -2531,7 +2554,7 @@
       <c r="C42" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D42" s="49" t="n">
         <v>0.04</v>
       </c>
       <c r="E42" s="18" t="n">
@@ -2571,7 +2594,7 @@
       <c r="C43" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="17" t="n">
+      <c r="D43" s="49" t="n">
         <v>5.87</v>
       </c>
       <c r="E43" s="18" t="n">
@@ -2612,7 +2635,7 @@
         <f>SUM(C4:C43)</f>
         <v/>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="50">
         <f>SUM(D4:D43)</f>
         <v/>
       </c>
@@ -2621,7 +2644,7 @@
         <v/>
       </c>
       <c r="F44" s="23">
-        <f>SUM(F4:F43)</f>
+        <f>SUMIF(E4:E43,"&gt;0",F4:F43)</f>
         <v/>
       </c>
       <c r="G44" s="24">
@@ -2656,7 +2679,7 @@
         <f>C44</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="51">
         <f>D44</f>
         <v/>
       </c>
@@ -2732,7 +2755,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="30" t="inlineStr">
         <is>
@@ -2740,7 +2762,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
@@ -13036,7 +13057,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -15564,7 +15584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="B1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -15579,7 +15599,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
       <c r="B3" s="44" t="inlineStr">
         <is>

--- a/docs/reports/daily/ER_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/ER_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Unified KPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="EB Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mode Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="KM Verification" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4923,7 +4923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5001,6 +5001,11 @@
           <t>Valid Trip?</t>
         </is>
       </c>
+      <c r="M5" s="14" t="inlineStr">
+        <is>
+          <t>Loco Travel</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
@@ -5057,6 +5062,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -5113,6 +5119,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -5169,6 +5176,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -5225,6 +5233,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -5281,6 +5290,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -5337,6 +5347,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M11" s="16" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -5393,6 +5404,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -5449,6 +5461,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -5505,6 +5518,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
@@ -5561,6 +5575,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -5617,6 +5632,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -5673,6 +5689,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
@@ -5729,6 +5746,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
@@ -5785,6 +5803,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
@@ -5841,6 +5860,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
@@ -5897,6 +5917,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
@@ -5953,6 +5974,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
@@ -6009,6 +6031,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -6065,6 +6088,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M24" s="16" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
@@ -6121,6 +6145,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -6177,6 +6202,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -6233,6 +6259,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
@@ -6289,6 +6316,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
@@ -6345,6 +6373,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
@@ -6401,6 +6430,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="31" t="inlineStr">
@@ -6457,6 +6487,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="31" t="inlineStr">
@@ -6513,6 +6544,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="31" t="inlineStr">
@@ -6569,6 +6601,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="31" t="inlineStr">
@@ -6625,6 +6658,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="31" t="inlineStr">
@@ -6681,6 +6715,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
@@ -6737,6 +6772,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="31" t="inlineStr">
@@ -6793,6 +6829,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="31" t="inlineStr">
@@ -6905,6 +6943,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -6961,6 +7000,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -7017,6 +7057,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -7073,6 +7114,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M42" s="16" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="31" t="inlineStr">
@@ -7129,6 +7171,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M43" s="16" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="31" t="inlineStr">
@@ -7185,6 +7228,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M44" s="16" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -7241,6 +7285,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="31" t="inlineStr">
@@ -7297,6 +7342,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M46" s="16" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -7353,6 +7399,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M47" s="16" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
@@ -7409,6 +7456,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M48" s="16" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
@@ -7465,6 +7513,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
@@ -7521,6 +7570,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M50" s="16" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
@@ -7577,6 +7627,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M51" s="16" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="31" t="inlineStr">
@@ -7633,6 +7684,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="31" t="inlineStr">
@@ -7689,6 +7741,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M53" s="16" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
@@ -7745,6 +7798,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
@@ -7801,6 +7855,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
@@ -7857,6 +7912,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M56" s="16" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
@@ -7913,6 +7969,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M57" s="16" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
@@ -7969,6 +8026,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M58" s="16" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
@@ -8025,6 +8083,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
@@ -8081,6 +8140,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
@@ -8137,6 +8197,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
@@ -8193,6 +8254,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
@@ -8249,6 +8311,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
@@ -8305,6 +8368,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
@@ -8361,6 +8425,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
@@ -8417,6 +8482,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M66" s="16" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
@@ -8473,6 +8539,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
@@ -8529,6 +8596,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
@@ -8585,6 +8653,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
@@ -8641,6 +8710,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M70" s="16" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
@@ -8697,6 +8767,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M71" s="16" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
@@ -8753,6 +8824,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M72" s="16" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
@@ -8809,6 +8881,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
@@ -8865,6 +8938,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
@@ -8921,6 +8995,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M75" s="16" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
@@ -8977,6 +9052,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M76" s="16" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
@@ -9033,6 +9109,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M77" s="16" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
@@ -9089,6 +9166,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M78" s="16" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
@@ -9145,6 +9223,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M79" s="16" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
@@ -9201,6 +9280,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M80" s="16" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
@@ -9257,6 +9337,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
@@ -9313,6 +9394,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M82" s="16" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
@@ -9369,6 +9451,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="31" t="inlineStr">
@@ -9425,6 +9508,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M84" s="16" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="31" t="inlineStr">
@@ -9481,6 +9565,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M85" s="16" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
@@ -9537,6 +9622,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M86" s="16" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="31" t="inlineStr">
@@ -9593,6 +9679,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M87" s="16" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="31" t="inlineStr">
@@ -9649,6 +9736,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M88" s="16" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="31" t="inlineStr">
@@ -9705,6 +9793,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="31" t="inlineStr">
@@ -9761,6 +9850,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M90" s="16" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="31" t="inlineStr">
@@ -9817,6 +9907,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M91" s="16" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="31" t="inlineStr">
@@ -9873,6 +9964,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M92" s="16" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="31" t="inlineStr">
@@ -9929,6 +10021,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M93" s="16" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="31" t="inlineStr">
@@ -9985,6 +10078,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M94" s="16" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="31" t="inlineStr">
@@ -10041,6 +10135,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M95" s="16" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="31" t="inlineStr">
@@ -10097,6 +10192,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M96" s="16" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="31" t="inlineStr">
@@ -10153,6 +10249,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M97" s="16" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="31" t="inlineStr">
@@ -10209,6 +10306,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M98" s="16" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="31" t="inlineStr">
@@ -10265,6 +10363,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M99" s="16" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="31" t="inlineStr">
@@ -10321,6 +10420,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M100" s="16" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="31" t="inlineStr">
@@ -10377,6 +10477,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M101" s="16" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
@@ -10433,6 +10534,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M102" s="16" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="31" t="inlineStr">
@@ -10489,6 +10591,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M103" s="16" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="31" t="inlineStr">
@@ -10545,6 +10648,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M104" s="16" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="31" t="inlineStr">
@@ -10601,6 +10705,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M105" s="16" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="31" t="inlineStr">
@@ -10657,6 +10762,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M106" s="16" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="31" t="inlineStr">
@@ -10713,6 +10819,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M107" s="16" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="31" t="inlineStr">
@@ -10769,6 +10876,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M108" s="16" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="31" t="inlineStr">
@@ -10825,6 +10933,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M109" s="16" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="31" t="inlineStr">
@@ -10881,6 +10990,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M110" s="16" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="31" t="inlineStr">
@@ -10937,6 +11047,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M111" s="16" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="31" t="inlineStr">
@@ -10993,6 +11104,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M112" s="16" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="31" t="inlineStr">
@@ -11049,6 +11161,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M113" s="16" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="31" t="inlineStr">
@@ -11105,6 +11218,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M114" s="16" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="31" t="inlineStr">
@@ -11161,6 +11275,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M115" s="16" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="31" t="inlineStr">
@@ -11217,6 +11332,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M116" s="16" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="31" t="inlineStr">
@@ -11273,6 +11389,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M117" s="16" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
@@ -11329,6 +11446,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M118" s="16" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="31" t="inlineStr">
@@ -11385,6 +11503,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M119" s="16" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="31" t="inlineStr">
@@ -11441,6 +11560,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M120" s="16" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="31" t="inlineStr">
@@ -11497,6 +11617,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M121" s="16" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="31" t="inlineStr">
@@ -11553,6 +11674,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M122" s="16" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="31" t="inlineStr">
@@ -11609,6 +11731,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M123" s="16" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="31" t="inlineStr">
@@ -11665,6 +11788,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M124" s="16" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="31" t="inlineStr">
@@ -11721,6 +11845,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M125" s="16" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="31" t="inlineStr">
@@ -11777,6 +11902,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M126" s="16" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="31" t="inlineStr">
@@ -11833,6 +11959,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M127" s="16" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="31" t="inlineStr">
@@ -11889,6 +12016,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M128" s="16" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="31" t="inlineStr">
@@ -11945,6 +12073,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M129" s="16" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="31" t="inlineStr">
@@ -12001,6 +12130,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M130" s="16" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="31" t="inlineStr">
@@ -12057,6 +12187,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M131" s="16" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="31" t="inlineStr">
@@ -12113,6 +12244,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M132" s="16" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="31" t="inlineStr">
@@ -12169,6 +12301,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M133" s="16" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
@@ -12225,6 +12358,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M134" s="16" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="31" t="inlineStr">
@@ -12281,6 +12415,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M135" s="16" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="31" t="inlineStr">
@@ -12337,6 +12472,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M136" s="16" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="31" t="inlineStr">
@@ -12393,6 +12529,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M137" s="16" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
@@ -12449,6 +12586,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M138" s="16" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="31" t="inlineStr">
@@ -12505,6 +12643,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M139" s="16" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="31" t="inlineStr">
@@ -12561,6 +12700,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M140" s="16" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="31" t="inlineStr">
@@ -12617,6 +12757,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M141" s="16" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="31" t="inlineStr">
@@ -12673,6 +12814,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M142" s="16" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="31" t="inlineStr">
@@ -12729,6 +12871,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M143" s="16" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="31" t="inlineStr">
@@ -12785,6 +12928,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M144" s="16" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="16" t="inlineStr">
@@ -12841,6 +12985,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M145" s="16" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="31" t="inlineStr">
@@ -12897,6 +13042,7 @@
           <t>Non-Valid</t>
         </is>
       </c>
+      <c r="M146" s="16" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="16" t="inlineStr">
@@ -12953,6 +13099,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M147" s="16" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="16" t="inlineStr">
@@ -13009,6 +13156,7 @@
           <t>Valid</t>
         </is>
       </c>
+      <c r="M148" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/docs/reports/daily/ER_Kavach_Unified_KPI_Jun30-Jun30.xlsx
+++ b/docs/reports/daily/ER_Kavach_Unified_KPI_Jun30-Jun30.xlsx
@@ -5062,7 +5062,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -5119,7 +5123,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -5176,7 +5184,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -5233,7 +5245,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M9" s="16" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -5290,7 +5306,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M10" s="16" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -5347,7 +5367,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -5404,7 +5428,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M12" s="16" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -5461,7 +5489,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -5518,7 +5550,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M14" s="16" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
@@ -5575,7 +5611,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -5632,7 +5672,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M16" s="16" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -5689,7 +5733,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
@@ -5746,7 +5794,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr">
+        <is>
+          <t>LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
@@ -5803,7 +5855,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
@@ -5860,7 +5916,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr">
+        <is>
+          <t>LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
@@ -5917,7 +5977,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M21" s="16" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
@@ -5974,7 +6038,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
@@ -6031,7 +6099,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -6088,7 +6160,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M24" s="16" t="inlineStr"/>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
@@ -6145,7 +6221,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -6202,7 +6282,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M26" s="16" t="inlineStr"/>
+      <c r="M26" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -6259,7 +6343,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M27" s="16" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
@@ -6316,7 +6404,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M28" s="16" t="inlineStr"/>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
@@ -6373,7 +6465,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M29" s="16" t="inlineStr"/>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
@@ -6430,7 +6526,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M30" s="16" t="inlineStr"/>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="31" t="inlineStr">
@@ -6487,7 +6587,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M31" s="16" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="31" t="inlineStr">
@@ -6544,7 +6648,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M32" s="16" t="inlineStr"/>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="31" t="inlineStr">
@@ -6601,7 +6709,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M33" s="16" t="inlineStr"/>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="31" t="inlineStr">
@@ -6658,7 +6770,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M34" s="16" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="31" t="inlineStr">
@@ -6715,7 +6831,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M35" s="16" t="inlineStr"/>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
@@ -6772,7 +6892,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M36" s="16" t="inlineStr"/>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="31" t="inlineStr">
@@ -6829,7 +6953,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M37" s="16" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
@@ -6886,7 +7014,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M38" s="16" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="31" t="inlineStr">
@@ -6943,7 +7075,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M39" s="16" t="inlineStr"/>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -7000,7 +7136,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M40" s="16" t="inlineStr"/>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -7057,7 +7197,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M41" s="16" t="inlineStr"/>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -7114,7 +7258,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M42" s="16" t="inlineStr"/>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="31" t="inlineStr">
@@ -7171,7 +7319,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M43" s="16" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="31" t="inlineStr">
@@ -7228,7 +7380,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M44" s="16" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -7285,7 +7441,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M45" s="16" t="inlineStr"/>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="31" t="inlineStr">
@@ -7342,7 +7502,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M46" s="16" t="inlineStr"/>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -7399,7 +7563,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M47" s="16" t="inlineStr"/>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
@@ -7456,7 +7624,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M48" s="16" t="inlineStr"/>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
@@ -7513,7 +7685,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M49" s="16" t="inlineStr"/>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
@@ -7570,7 +7746,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M50" s="16" t="inlineStr"/>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
@@ -7627,7 +7807,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M51" s="16" t="inlineStr"/>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="31" t="inlineStr">
@@ -7684,7 +7868,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M52" s="16" t="inlineStr"/>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="31" t="inlineStr">
@@ -7741,7 +7929,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M53" s="16" t="inlineStr"/>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
@@ -7798,7 +7990,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M54" s="16" t="inlineStr"/>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
@@ -7855,7 +8051,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M55" s="16" t="inlineStr"/>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
@@ -7912,7 +8112,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M56" s="16" t="inlineStr"/>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
@@ -7969,7 +8173,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M57" s="16" t="inlineStr"/>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
@@ -8026,7 +8234,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M58" s="16" t="inlineStr"/>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
@@ -8083,7 +8295,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M59" s="16" t="inlineStr"/>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
@@ -8140,7 +8356,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M60" s="16" t="inlineStr"/>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
@@ -8197,7 +8417,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M61" s="16" t="inlineStr"/>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
@@ -8254,7 +8478,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M62" s="16" t="inlineStr"/>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
@@ -8311,7 +8539,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M63" s="16" t="inlineStr"/>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
@@ -8368,7 +8600,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M64" s="16" t="inlineStr"/>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
@@ -8425,7 +8661,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M65" s="16" t="inlineStr"/>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
@@ -8482,7 +8722,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M66" s="16" t="inlineStr"/>
+      <c r="M66" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
@@ -8539,7 +8783,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M67" s="16" t="inlineStr"/>
+      <c r="M67" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
@@ -8596,7 +8844,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M68" s="16" t="inlineStr"/>
+      <c r="M68" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
@@ -8653,7 +8905,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M69" s="16" t="inlineStr"/>
+      <c r="M69" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
@@ -8710,7 +8966,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M70" s="16" t="inlineStr"/>
+      <c r="M70" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
@@ -8767,7 +9027,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M71" s="16" t="inlineStr"/>
+      <c r="M71" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
@@ -8824,7 +9088,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M72" s="16" t="inlineStr"/>
+      <c r="M72" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
@@ -8881,7 +9149,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M73" s="16" t="inlineStr"/>
+      <c r="M73" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
@@ -8938,7 +9210,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M74" s="16" t="inlineStr"/>
+      <c r="M74" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
@@ -8995,7 +9271,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M75" s="16" t="inlineStr"/>
+      <c r="M75" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
@@ -9052,7 +9332,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M76" s="16" t="inlineStr"/>
+      <c r="M76" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
@@ -9109,7 +9393,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M77" s="16" t="inlineStr"/>
+      <c r="M77" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
@@ -9166,7 +9454,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M78" s="16" t="inlineStr"/>
+      <c r="M78" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
@@ -9223,7 +9515,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M79" s="16" t="inlineStr"/>
+      <c r="M79" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
@@ -9280,7 +9576,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M80" s="16" t="inlineStr"/>
+      <c r="M80" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
@@ -9337,7 +9637,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M81" s="16" t="inlineStr"/>
+      <c r="M81" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
@@ -9394,7 +9698,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M82" s="16" t="inlineStr"/>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
@@ -9451,7 +9759,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M83" s="16" t="inlineStr"/>
+      <c r="M83" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="31" t="inlineStr">
@@ -9508,7 +9820,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M84" s="16" t="inlineStr"/>
+      <c r="M84" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="31" t="inlineStr">
@@ -9565,7 +9881,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M85" s="16" t="inlineStr"/>
+      <c r="M85" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
@@ -9622,7 +9942,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M86" s="16" t="inlineStr"/>
+      <c r="M86" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="31" t="inlineStr">
@@ -9679,7 +10003,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M87" s="16" t="inlineStr"/>
+      <c r="M87" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="31" t="inlineStr">
@@ -9736,7 +10064,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M88" s="16" t="inlineStr"/>
+      <c r="M88" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="31" t="inlineStr">
@@ -9793,7 +10125,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M89" s="16" t="inlineStr"/>
+      <c r="M89" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="31" t="inlineStr">
@@ -9850,7 +10186,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M90" s="16" t="inlineStr"/>
+      <c r="M90" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="31" t="inlineStr">
@@ -9907,7 +10247,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M91" s="16" t="inlineStr"/>
+      <c r="M91" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="31" t="inlineStr">
@@ -9964,7 +10308,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M92" s="16" t="inlineStr"/>
+      <c r="M92" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="31" t="inlineStr">
@@ -10021,7 +10369,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M93" s="16" t="inlineStr"/>
+      <c r="M93" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="31" t="inlineStr">
@@ -10078,7 +10430,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M94" s="16" t="inlineStr"/>
+      <c r="M94" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="31" t="inlineStr">
@@ -10135,7 +10491,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M95" s="16" t="inlineStr"/>
+      <c r="M95" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="31" t="inlineStr">
@@ -10192,7 +10552,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M96" s="16" t="inlineStr"/>
+      <c r="M96" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="31" t="inlineStr">
@@ -10249,7 +10613,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M97" s="16" t="inlineStr"/>
+      <c r="M97" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="31" t="inlineStr">
@@ -10306,7 +10674,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M98" s="16" t="inlineStr"/>
+      <c r="M98" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="31" t="inlineStr">
@@ -10363,7 +10735,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M99" s="16" t="inlineStr"/>
+      <c r="M99" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="31" t="inlineStr">
@@ -10420,7 +10796,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M100" s="16" t="inlineStr"/>
+      <c r="M100" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="31" t="inlineStr">
@@ -10477,7 +10857,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M101" s="16" t="inlineStr"/>
+      <c r="M101" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
@@ -10534,7 +10918,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M102" s="16" t="inlineStr"/>
+      <c r="M102" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="31" t="inlineStr">
@@ -10591,7 +10979,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M103" s="16" t="inlineStr"/>
+      <c r="M103" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="31" t="inlineStr">
@@ -10648,7 +11040,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M104" s="16" t="inlineStr"/>
+      <c r="M104" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="31" t="inlineStr">
@@ -10705,7 +11101,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M105" s="16" t="inlineStr"/>
+      <c r="M105" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="31" t="inlineStr">
@@ -10762,7 +11162,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M106" s="16" t="inlineStr"/>
+      <c r="M106" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="31" t="inlineStr">
@@ -10819,7 +11223,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M107" s="16" t="inlineStr"/>
+      <c r="M107" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="31" t="inlineStr">
@@ -10876,7 +11284,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M108" s="16" t="inlineStr"/>
+      <c r="M108" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="31" t="inlineStr">
@@ -10933,7 +11345,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M109" s="16" t="inlineStr"/>
+      <c r="M109" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="31" t="inlineStr">
@@ -10990,7 +11406,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M110" s="16" t="inlineStr"/>
+      <c r="M110" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="31" t="inlineStr">
@@ -11047,7 +11467,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M111" s="16" t="inlineStr"/>
+      <c r="M111" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="31" t="inlineStr">
@@ -11104,7 +11528,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M112" s="16" t="inlineStr"/>
+      <c r="M112" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="31" t="inlineStr">
@@ -11161,7 +11589,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M113" s="16" t="inlineStr"/>
+      <c r="M113" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="31" t="inlineStr">
@@ -11218,7 +11650,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M114" s="16" t="inlineStr"/>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="31" t="inlineStr">
@@ -11275,7 +11711,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M115" s="16" t="inlineStr"/>
+      <c r="M115" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="31" t="inlineStr">
@@ -11332,7 +11772,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M116" s="16" t="inlineStr"/>
+      <c r="M116" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="31" t="inlineStr">
@@ -11389,7 +11833,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M117" s="16" t="inlineStr"/>
+      <c r="M117" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="31" t="inlineStr">
@@ -11446,7 +11894,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M118" s="16" t="inlineStr"/>
+      <c r="M118" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="31" t="inlineStr">
@@ -11503,7 +11955,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M119" s="16" t="inlineStr"/>
+      <c r="M119" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="31" t="inlineStr">
@@ -11560,7 +12016,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M120" s="16" t="inlineStr"/>
+      <c r="M120" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="31" t="inlineStr">
@@ -11617,7 +12077,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M121" s="16" t="inlineStr"/>
+      <c r="M121" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="31" t="inlineStr">
@@ -11674,7 +12138,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M122" s="16" t="inlineStr"/>
+      <c r="M122" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="31" t="inlineStr">
@@ -11731,7 +12199,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M123" s="16" t="inlineStr"/>
+      <c r="M123" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="31" t="inlineStr">
@@ -11788,7 +12260,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M124" s="16" t="inlineStr"/>
+      <c r="M124" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="31" t="inlineStr">
@@ -11845,7 +12321,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M125" s="16" t="inlineStr"/>
+      <c r="M125" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="31" t="inlineStr">
@@ -11902,7 +12382,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M126" s="16" t="inlineStr"/>
+      <c r="M126" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="31" t="inlineStr">
@@ -11959,7 +12443,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M127" s="16" t="inlineStr"/>
+      <c r="M127" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="31" t="inlineStr">
@@ -12016,7 +12504,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M128" s="16" t="inlineStr"/>
+      <c r="M128" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="31" t="inlineStr">
@@ -12073,7 +12565,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M129" s="16" t="inlineStr"/>
+      <c r="M129" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="31" t="inlineStr">
@@ -12130,7 +12626,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M130" s="16" t="inlineStr"/>
+      <c r="M130" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="31" t="inlineStr">
@@ -12187,7 +12687,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M131" s="16" t="inlineStr"/>
+      <c r="M131" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="31" t="inlineStr">
@@ -12244,7 +12748,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M132" s="16" t="inlineStr"/>
+      <c r="M132" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="31" t="inlineStr">
@@ -12301,7 +12809,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M133" s="16" t="inlineStr"/>
+      <c r="M133" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
@@ -12358,7 +12870,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M134" s="16" t="inlineStr"/>
+      <c r="M134" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="31" t="inlineStr">
@@ -12415,7 +12931,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M135" s="16" t="inlineStr"/>
+      <c r="M135" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="31" t="inlineStr">
@@ -12472,7 +12992,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M136" s="16" t="inlineStr"/>
+      <c r="M136" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="31" t="inlineStr">
@@ -12529,7 +13053,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M137" s="16" t="inlineStr"/>
+      <c r="M137" s="16" t="inlineStr">
+        <is>
+          <t>LC-59, Khana Jn, Khana Link, Galsi</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
@@ -12586,7 +13114,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M138" s="16" t="inlineStr"/>
+      <c r="M138" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="31" t="inlineStr">
@@ -12643,7 +13175,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M139" s="16" t="inlineStr"/>
+      <c r="M139" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="31" t="inlineStr">
@@ -12700,7 +13236,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M140" s="16" t="inlineStr"/>
+      <c r="M140" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="31" t="inlineStr">
@@ -12757,7 +13297,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M141" s="16" t="inlineStr"/>
+      <c r="M141" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="31" t="inlineStr">
@@ -12814,7 +13358,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M142" s="16" t="inlineStr"/>
+      <c r="M142" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="31" t="inlineStr">
@@ -12871,7 +13419,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M143" s="16" t="inlineStr"/>
+      <c r="M143" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="31" t="inlineStr">
@@ -12928,7 +13480,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M144" s="16" t="inlineStr"/>
+      <c r="M144" s="16" t="inlineStr">
+        <is>
+          <t>Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="16" t="inlineStr">
@@ -12985,7 +13541,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M145" s="16" t="inlineStr"/>
+      <c r="M145" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="31" t="inlineStr">
@@ -13042,7 +13602,11 @@
           <t>Non-Valid</t>
         </is>
       </c>
-      <c r="M146" s="16" t="inlineStr"/>
+      <c r="M146" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="16" t="inlineStr">
@@ -13099,7 +13663,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M147" s="16" t="inlineStr"/>
+      <c r="M147" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="16" t="inlineStr">
@@ -13156,7 +13724,11 @@
           <t>Valid</t>
         </is>
       </c>
-      <c r="M148" s="16" t="inlineStr"/>
+      <c r="M148" s="16" t="inlineStr">
+        <is>
+          <t>Howrah, Howrah Sorting Yard, Liluah, Belur, Bally, Belanagar, Dankuni, LC-12, Janai Road, Baruipara, Kamarkundu, LC-31, Chandanpur, LC-38, Belmuri, Cheragram, LC-41, Gurap, LC-48, Jaugram, LC-57, Masagram, Palla Road, Saktigarh, Gangpur, Barddhaman Jn, Talit, LC-59, Khana Jn, Khana Link, Galsi, LC-83, Paraj, Mankar, LC-96, Panagarh, LC-105, Rajbandh, LC-111, Durgapur, DCOP, Waria, Andal East Outer, Andal, Baktarnagar B H, Raniganj, Nimcha B H, Ratibati, Kaliphari, Asansol, Barachak Jn, Sitarampur Central, Kulti, Barakar, Kumardubi, Mugma, Thaparnagar, Kalubathan, LC-12, Chhota Ambana</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
